--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>12:52</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -478,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,10 +500,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -528,22 +539,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>56</v>
@@ -560,13 +577,19 @@
       <c r="J2">
         <v>94.64</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
         <v>110213</v>
       </c>
+      <c r="M2">
+        <v>137423</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -574,18 +597,18 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>7</v>
@@ -594,9 +617,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>56</v>
@@ -614,9 +637,9 @@
         <v>94.64</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>56</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -49,25 +49,19 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>В3650ВХ</t>
-  </si>
-  <si>
-    <t>78970155027720808</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>В5689ВН</t>
+  </si>
+  <si>
+    <t>78970155027720790</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>12:52</t>
+    <t>2026-06-23 09:18:29</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -487,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,12 +494,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,57 +531,45 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46196</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>9.01</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H2">
+        <v>13.42</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J2">
+        <v>13.7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="F2">
-        <v>56</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H2">
-        <v>92.95999999999999</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J2">
-        <v>94.64</v>
-      </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2">
-        <v>110213</v>
-      </c>
-      <c r="M2">
-        <v>137423</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -597,18 +577,18 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:11">
       <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>7</v>
@@ -617,42 +597,42 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="7">
-        <v>56</v>
+        <v>9.01</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="8">
-        <v>1.66</v>
+        <v>1.4895</v>
       </c>
       <c r="E7" s="7">
-        <v>92.95999999999999</v>
+        <v>13.42</v>
       </c>
       <c r="F7" s="7">
-        <v>94.64</v>
+        <v>13.7</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:11">
       <c r="A8" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" s="10">
-        <v>56</v>
+        <v>9.01</v>
       </c>
       <c r="C8" s="10">
         <v>1</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="10">
-        <v>92.95999999999999</v>
+        <v>13.42</v>
       </c>
       <c r="F8" s="10">
-        <v>94.64</v>
+        <v>13.7</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В5689ВН</t>
@@ -61,7 +70,13 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-23 09:18:29</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:18:00</t>
+  </si>
+  <si>
+    <t>3233765335 3233765335</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -481,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -490,14 +505,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,45 +549,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46196</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>9.01</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
         <v>1.49</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>13.42</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>13.7</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>68591</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -577,29 +613,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="7">
         <v>9.01</v>
@@ -617,9 +653,9 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="10">
         <v>9.01</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В5689ВН</t>
@@ -70,13 +67,7 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:18:00</t>
-  </si>
-  <si>
-    <t>3233765335 3233765335</t>
+    <t>09:19</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -496,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,57 +545,51 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46196</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>9.01</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H2">
+        <v>13.42</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J2">
+        <v>13.7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>68591</v>
+      </c>
+      <c r="M2">
+        <v>222811</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="H2">
-        <v>1.49</v>
-      </c>
-      <c r="I2" s="1">
-        <v>13.42</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
-        <v>13.7</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>68591</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -613,29 +597,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>9.01</v>
@@ -653,9 +637,9 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>9.01</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -116,7 +116,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -700,7 +700,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>1.6101</v>
+        <v>1.610087</v>
       </c>
       <c r="E8" s="7">
         <v>172.07</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -508,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,13 +524,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,98 +573,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>60.87</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
+        <v>1.499</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.58</v>
       </c>
-      <c r="I2" s="1">
-        <v>96.17</v>
-      </c>
       <c r="J2">
+        <v>96.1746</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
-        <v>98</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>98.00069999999999</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2">
         <v>110684</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
+      <c r="O2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46223</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
+        <v>1.546</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.65</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>75.90000000000001</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>1.68</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>77.28</v>
       </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
         <v>69340</v>
       </c>
-      <c r="N3" t="s">
-        <v>24</v>
+      <c r="O3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -669,29 +681,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="7">
         <v>106.87</v>
@@ -700,7 +712,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>1.610087</v>
+        <v>1.61013</v>
       </c>
       <c r="E8" s="7">
         <v>172.07</v>
@@ -709,9 +721,9 @@
         <v>175.28</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="10">
         <v>106.87</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -117,9 +114,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -213,10 +210,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -524,13 +521,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,107 +570,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>60.87</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>1.58</v>
+      </c>
+      <c r="I2" s="1">
+        <v>96.175</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>98.001</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J2">
-        <v>96.1746</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>98.00069999999999</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>110684</v>
       </c>
-      <c r="O2" t="s">
-        <v>24</v>
+      <c r="N2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46223</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3">
         <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I3" s="1">
-        <v>1.65</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="J3">
-        <v>75.90000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="K3" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L3" s="1">
         <v>77.28</v>
       </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>69340</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -681,49 +669,49 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7">
         <v>106.87</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>1.61013</v>
-      </c>
-      <c r="E8" s="7">
-        <v>172.07</v>
-      </c>
-      <c r="F8" s="7">
-        <v>175.28</v>
+        <v>1.61</v>
+      </c>
+      <c r="E8" s="8">
+        <v>172.075</v>
+      </c>
+      <c r="F8" s="8">
+        <v>175.281</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10">
         <v>106.87</v>
@@ -733,10 +721,10 @@
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="10">
-        <v>172.07</v>
+        <v>172.075</v>
       </c>
       <c r="F9" s="10">
-        <v>175.28</v>
+        <v>175.281</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,37 +55,19 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>В3650ВХ</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В5689ВН</t>
   </si>
   <si>
-    <t>78970155027720808</t>
-  </si>
-  <si>
     <t>78970155027720790</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>09:23:00</t>
-  </si>
-  <si>
-    <t>10:06:00</t>
-  </si>
-  <si>
-    <t>3234885648 3234885648</t>
-  </si>
-  <si>
-    <t>3235093075 3235093075</t>
+    <t>10:31</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -114,9 +93,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -210,10 +189,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,169 +545,119 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>40.279</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="H2">
+        <v>70.89100000000001</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="J2">
+        <v>72.099</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>69854</v>
+      </c>
+      <c r="M2">
+        <v>241591</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>60.87</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.58</v>
-      </c>
-      <c r="I2" s="1">
-        <v>96.175</v>
-      </c>
-      <c r="J2">
-        <v>1.61</v>
-      </c>
-      <c r="K2" s="1">
-        <v>98.001</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M2">
-        <v>110684</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7">
+        <v>40.279</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1.76</v>
+      </c>
+      <c r="E7" s="7">
+        <v>70.89</v>
+      </c>
+      <c r="F7" s="7">
+        <v>72.099</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46223</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>1.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="J3">
-        <v>1.68</v>
-      </c>
-      <c r="K3" s="1">
-        <v>77.28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
-        <v>69340</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7">
-        <v>106.87</v>
-      </c>
-      <c r="C8" s="8">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.61</v>
-      </c>
-      <c r="E8" s="8">
-        <v>172.075</v>
-      </c>
-      <c r="F8" s="8">
-        <v>175.281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="10">
-        <v>106.87</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>172.075</v>
-      </c>
-      <c r="F9" s="10">
-        <v>175.281</v>
+      <c r="B8" s="10">
+        <v>40.279</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>70.89</v>
+      </c>
+      <c r="F8" s="10">
+        <v>72.099</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,7 +58,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>В5689ВН</t>
@@ -67,7 +73,19 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>10:31</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:53:00</t>
+  </si>
+  <si>
+    <t>11:22:00</t>
+  </si>
+  <si>
+    <t>3236520848 3236520848</t>
+  </si>
+  <si>
+    <t>3237062867 3237062867</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДС</t>
@@ -92,10 +110,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -175,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -189,10 +208,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -496,16 +517,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -545,119 +567,169 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>47.05</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.657</v>
+      </c>
+      <c r="I2" s="1">
+        <v>77.962</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="K2" s="1">
+        <v>84.69</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>70285</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="F2">
-        <v>40.279</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H2">
-        <v>70.89100000000001</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J2">
-        <v>72.099</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
-        <v>69854</v>
-      </c>
-      <c r="M2">
-        <v>241591</v>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>51.64</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.719</v>
+      </c>
+      <c r="I3" s="1">
+        <v>88.76900000000001</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K3" s="1">
+        <v>95.53400000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>70782</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="B8" s="7">
+        <v>98.69</v>
+      </c>
+      <c r="C8" s="8">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1.68944</v>
+      </c>
+      <c r="E8" s="7">
+        <v>166.73</v>
+      </c>
+      <c r="F8" s="7">
+        <v>180.22</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="7">
-        <v>40.279</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1.76</v>
-      </c>
-      <c r="E7" s="7">
-        <v>70.89</v>
-      </c>
-      <c r="F7" s="7">
-        <v>72.099</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="10">
-        <v>40.279</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>70.89</v>
-      </c>
-      <c r="F8" s="10">
-        <v>72.099</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="11">
+        <v>98.69</v>
+      </c>
+      <c r="C9" s="12">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="11">
+        <v>166.73</v>
+      </c>
+      <c r="F9" s="11">
+        <v>180.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДС/КСУДС.xlsx
@@ -594,10 +594,10 @@
         <v>19</v>
       </c>
       <c r="H2" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I2" s="1">
-        <v>77.962</v>
+        <v>83.27800000000001</v>
       </c>
       <c r="J2" s="1">
         <v>1.8</v>
@@ -638,10 +638,10 @@
         <v>19</v>
       </c>
       <c r="H3" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I3" s="1">
-        <v>88.76900000000001</v>
+        <v>93.985</v>
       </c>
       <c r="J3" s="1">
         <v>1.85</v>
@@ -700,10 +700,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="9">
-        <v>1.68944</v>
+        <v>1.79616</v>
       </c>
       <c r="E8" s="7">
-        <v>166.73</v>
+        <v>177.26</v>
       </c>
       <c r="F8" s="7">
         <v>180.22</v>
@@ -721,7 +721,7 @@
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="11">
-        <v>166.73</v>
+        <v>177.26</v>
       </c>
       <c r="F9" s="11">
         <v>180.22</v>
